--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c5144fadc8a1016e</t>
+          <t>a078c161cdef4877</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a078c161cdef4877</t>
+          <t>f15ec97e72813ff5</t>
         </is>
       </c>
     </row>
